--- a/demo-data/Approver_Roster.xlsx
+++ b/demo-data/Approver_Roster.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approver Roster" sheetId="1" r:id="Rc312692cbb2f440c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approver Roster" sheetId="1" r:id="Ra94b9ef401a74c32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -30,8 +30,26 @@
       <x:color rgb="FF334155"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF475569"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -46,6 +64,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFEEF3F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F6B82"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF174F73"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -55,7 +83,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -68,6 +96,23 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -78,7 +123,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ApproverRoster" displayName="ApproverRoster" ref="A4:D10" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ApproverRoster" displayName="ApproverRoster" ref="A4:D9" headerRowCount="1">
+  <x:autoFilter ref="A4:D9"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Role"/>
     <x:tableColumn id="2" name="Primary Approver"/>
@@ -284,39 +330,39 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="31" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="27" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25.6299991607666" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="13" t="str">
         <x:v>Approver Roster</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
+      <x:c r="B1" s="13"/>
+      <x:c r="C1" s="13"/>
+      <x:c r="D1" s="13"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="7" t="str">
+      <x:c r="A2" s="14" t="str">
         <x:v>Primary approvers, delegates, and target response times used by approval routing.</x:v>
       </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
+      <x:c r="B2" s="14"/>
+      <x:c r="C2" s="14"/>
+      <x:c r="D2" s="14"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="str">
+      <x:c r="A4" s="11" t="str">
         <x:v>Role</x:v>
       </x:c>
-      <x:c r="B4" t="str">
+      <x:c r="B4" s="11" t="str">
         <x:v>Primary Approver</x:v>
       </x:c>
-      <x:c r="C4" t="str">
+      <x:c r="C4" s="11" t="str">
         <x:v>Delegate Approver</x:v>
       </x:c>
-      <x:c r="D4" t="str">
+      <x:c r="D4" s="11" t="str">
         <x:v>Target Response Time (Hours)</x:v>
       </x:c>
     </x:row>
@@ -336,27 +382,27 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>Supply Chain Manager</x:v>
+        <x:v>Pricing Governance Owner</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>Elena Rossi</x:v>
+        <x:v>Priya Nair</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>Jordan Blake</x:v>
+        <x:v>Daniel Ortiz</x:v>
       </x:c>
       <x:c r="D6" t="n">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>Pricing Governance Owner</x:v>
+        <x:v>Finance Director</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>Priya Nair</x:v>
+        <x:v>Daniel Ortiz</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>Marcus Reed</x:v>
+        <x:v>Sarah Morgan</x:v>
       </x:c>
       <x:c r="D7" t="n">
         <x:v>48</x:v>
@@ -364,45 +410,37 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>Market Access Director</x:v>
+        <x:v>Operations Manager</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>Marcus Reed</x:v>
+        <x:v>Elena Rossi</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>Priya Nair</x:v>
+        <x:v>Jordan Blake</x:v>
       </x:c>
       <x:c r="D8" t="n">
-        <x:v>48</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>Finance Director</x:v>
+        <x:v>General Manager</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>Daniel Ortiz</x:v>
+        <x:v>Sarah Morgan</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>Sarah Morgan</x:v>
+        <x:v>Admin User</x:v>
       </x:c>
       <x:c r="D9" t="n">
-        <x:v>48</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>General Manager</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>Sarah Morgan</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>Admin User</x:v>
-      </x:c>
-      <x:c r="D10" t="n">
-        <x:v>72</x:v>
-      </x:c>
+      <x:c r="A10"/>
+      <x:c r="B10"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -411,7 +449,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31694f5c4f0b4067"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9be91a02bd04d40"/>
   </x:tableParts>
 </x:worksheet>
 </file>